--- a/hardware/SPI NAND Flash Breakout Board/8 Gb/v0.1.0/spi_nand_bom.xlsx
+++ b/hardware/SPI NAND Flash Breakout Board/8 Gb/v0.1.0/spi_nand_bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/8 GBit/v0.1.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/dstjohn_email_sc_edu/Documents/Desktop/Edge-Computing-Power-Management-Development-Kit/hardware/SPI NAND Flash Breakout Board/8 Gb/v0.1.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="98" documentId="11_5A4B2C90D3AEA2794F446FDFF5D8B87F547F059E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED232BE9-85F5-4EDC-B549-2D266777E142}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="3" r:id="rId1"/>
